--- a/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T08:07:01+00:00</t>
+    <t>2026-05-12T10:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T10:20:43+00:00</t>
+    <t>2026-05-18T14:59:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:59:07+00:00</t>
+    <t>2026-05-20T10:28:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T10:28:07+00:00</t>
+    <t>2026-05-20T13:59:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T13:59:21+00:00</t>
+    <t>2026-05-21T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T14:19:44+00:00</t>
+    <t>2026-05-26T06:52:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T06:52:09+00:00</t>
+    <t>2026-05-27T13:31:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:31:13+00:00</t>
+    <t>2026-05-28T06:55:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-MAI-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T06:55:04+00:00</t>
+    <t>2026-05-29T07:18:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
